--- a/Res_ConvLSTM/DroughtDataset_model_testing_1754031464_h_9.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1754031464_h_9.xlsx
@@ -652,13 +652,13 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.02880319171364172</v>
+        <v>0.02416511822683657</v>
       </c>
       <c r="B2" t="n">
-        <v>0.008458258475039731</v>
+        <v>0.008452235047349248</v>
       </c>
       <c r="C2" t="n">
-        <v>56666493</v>
+        <v>6312978</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>56666493</v>
+        <v>6312978</v>
       </c>
       <c r="K2" t="n">
-        <v>38512110</v>
+        <v>4162508</v>
       </c>
       <c r="L2" t="n">
-        <v>20411905</v>
+        <v>1775525</v>
       </c>
       <c r="M2" t="n">
-        <v>4691092</v>
+        <v>304730</v>
       </c>
       <c r="N2" t="n">
-        <v>185852</v>
+        <v>8539</v>
       </c>
       <c r="O2" t="n">
-        <v>2893818</v>
+        <v>213171</v>
       </c>
       <c r="P2" t="n">
-        <v>1109858</v>
+        <v>63288</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9999849200248718</v>
+        <v>0.9999667406082153</v>
       </c>
       <c r="R2" t="n">
-        <v>0.8339129090309143</v>
+        <v>0.7413588166236877</v>
       </c>
       <c r="S2" t="n">
-        <v>0.6890178322792053</v>
+        <v>0.5723438262939453</v>
       </c>
       <c r="T2" t="n">
-        <v>0.6138835549354553</v>
+        <v>0.4606707394123077</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2638841271400452</v>
+        <v>0.07105530053377151</v>
       </c>
       <c r="V2" t="n">
-        <v>0.666997492313385</v>
+        <v>0.5026906728744507</v>
       </c>
       <c r="W2" t="n">
-        <v>0.782322883605957</v>
+        <v>0.6748200654983521</v>
       </c>
       <c r="X2" t="n">
-        <v>56666493</v>
+        <v>6312978</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,469 +742,469 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>56666493</v>
+        <v>6312978</v>
       </c>
       <c r="AF2" t="n">
-        <v>43037872</v>
+        <v>4763805</v>
       </c>
       <c r="AG2" t="n">
-        <v>26773490</v>
+        <v>3006353</v>
       </c>
       <c r="AH2" t="n">
-        <v>7206453</v>
+        <v>805109</v>
       </c>
       <c r="AI2" t="n">
-        <v>530962</v>
+        <v>59219</v>
       </c>
       <c r="AJ2" t="n">
-        <v>4135986</v>
+        <v>460827</v>
       </c>
       <c r="AK2" t="n">
-        <v>1621076</v>
+        <v>180323</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.9559941291809082</v>
+        <v>0.9549221992492676</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.9116339683532715</v>
+        <v>0.912146270275116</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.8583457469940186</v>
+        <v>0.8583800792694092</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.661908745765686</v>
+        <v>0.6608968377113342</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.9020386338233948</v>
+        <v>0.9020029902458191</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.9314467906951904</v>
+        <v>0.9314685463905334</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.00746180744694742</v>
+        <v>0.006133507722881389</v>
       </c>
       <c r="B3" t="n">
-        <v>0.002028316989047001</v>
+        <v>0.002026323576521127</v>
       </c>
       <c r="C3" t="n">
-        <v>429</v>
+        <v>17</v>
       </c>
       <c r="D3" t="n">
-        <v>38512110</v>
+        <v>4162508</v>
       </c>
       <c r="E3" t="n">
-        <v>6235254</v>
+        <v>785221</v>
       </c>
       <c r="F3" t="n">
-        <v>171785</v>
+        <v>23651</v>
       </c>
       <c r="G3" t="n">
-        <v>13313</v>
+        <v>2252</v>
       </c>
       <c r="H3" t="n">
-        <v>12228</v>
+        <v>1947</v>
       </c>
       <c r="I3" t="n">
-        <v>510</v>
+        <v>59</v>
       </c>
       <c r="J3" t="n">
-        <v>89910254</v>
+        <v>10016412</v>
       </c>
       <c r="K3" t="n">
-        <v>93961669</v>
+        <v>9901752</v>
       </c>
       <c r="L3" t="n">
-        <v>107936681</v>
+        <v>11696601</v>
       </c>
       <c r="M3" t="n">
-        <v>135221587</v>
+        <v>15032959</v>
       </c>
       <c r="N3" t="n">
-        <v>145256190</v>
+        <v>16128268</v>
       </c>
       <c r="O3" t="n">
-        <v>140544767</v>
+        <v>15607330</v>
       </c>
       <c r="P3" t="n">
-        <v>144527980</v>
+        <v>16105417</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.8568599820137024</v>
+        <v>0.836574912071228</v>
       </c>
       <c r="S3" t="n">
-        <v>0.693617582321167</v>
+        <v>0.5370087623596191</v>
       </c>
       <c r="T3" t="n">
-        <v>0.5581018328666687</v>
+        <v>0.324222594499588</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2314562946557999</v>
+        <v>0.09519828110933304</v>
       </c>
       <c r="V3" t="n">
-        <v>0.6307256817817688</v>
+        <v>0.4168535768985748</v>
       </c>
       <c r="W3" t="n">
-        <v>0.6375533938407898</v>
+        <v>0.3267556726932526</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>43037872</v>
+        <v>4763805</v>
       </c>
       <c r="Z3" t="n">
-        <v>1770047</v>
+        <v>196543</v>
       </c>
       <c r="AA3" t="n">
-        <v>76085</v>
+        <v>8427</v>
       </c>
       <c r="AB3" t="n">
-        <v>61120</v>
+        <v>6839</v>
       </c>
       <c r="AC3" t="n">
-        <v>235</v>
+        <v>11</v>
       </c>
       <c r="AD3" t="n">
-        <v>270</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
-        <v>89911107</v>
+        <v>10016622</v>
       </c>
       <c r="AF3" t="n">
-        <v>99650873</v>
+        <v>11129066</v>
       </c>
       <c r="AG3" t="n">
-        <v>114554222</v>
+        <v>12733718</v>
       </c>
       <c r="AH3" t="n">
-        <v>136982866</v>
+        <v>15256890</v>
       </c>
       <c r="AI3" t="n">
-        <v>145503426</v>
+        <v>16209518</v>
       </c>
       <c r="AJ3" t="n">
-        <v>141540355</v>
+        <v>15768153</v>
       </c>
       <c r="AK3" t="n">
-        <v>144717483</v>
+        <v>16122647</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.9575541019439697</v>
+        <v>0.95742267370224</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.9097907543182373</v>
+        <v>0.9092735648155212</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.8573557138442993</v>
+        <v>0.8566092252731323</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.6612492799758911</v>
+        <v>0.6602116227149963</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.9014639258384705</v>
+        <v>0.9011421799659729</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.9312204718589783</v>
+        <v>0.931006908416748</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.06651468065354633</v>
+        <v>0.05786427574638871</v>
       </c>
       <c r="B4" t="n">
-        <v>0.0319910069736064</v>
+        <v>0.03197108341586186</v>
       </c>
       <c r="C4" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D4" t="n">
-        <v>7115738</v>
+        <v>1325012</v>
       </c>
       <c r="E4" t="n">
-        <v>20411905</v>
+        <v>1775525</v>
       </c>
       <c r="F4" t="n">
-        <v>1619999</v>
+        <v>159608</v>
       </c>
       <c r="G4" t="n">
-        <v>75880</v>
+        <v>15652</v>
       </c>
       <c r="H4" t="n">
-        <v>188314</v>
+        <v>28401</v>
       </c>
       <c r="I4" t="n">
-        <v>16337</v>
+        <v>2113</v>
       </c>
       <c r="J4" t="n">
-        <v>853</v>
+        <v>210</v>
       </c>
       <c r="K4" t="n">
-        <v>7670302</v>
+        <v>1452193</v>
       </c>
       <c r="L4" t="n">
-        <v>9212735</v>
+        <v>1326675</v>
       </c>
       <c r="M4" t="n">
-        <v>2950572</v>
+        <v>356762</v>
       </c>
       <c r="N4" t="n">
-        <v>518442</v>
+        <v>111635</v>
       </c>
       <c r="O4" t="n">
-        <v>1444756</v>
+        <v>210889</v>
       </c>
       <c r="P4" t="n">
-        <v>308812</v>
+        <v>30497</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9999924302101135</v>
+        <v>0.9999833703041077</v>
       </c>
       <c r="R4" t="n">
-        <v>0.845230758190155</v>
+        <v>0.786094069480896</v>
       </c>
       <c r="S4" t="n">
-        <v>0.6913100481033325</v>
+        <v>0.5541135668754578</v>
       </c>
       <c r="T4" t="n">
-        <v>0.5846651792526245</v>
+        <v>0.3805864155292511</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2466087639331818</v>
+        <v>0.08137379586696625</v>
       </c>
       <c r="V4" t="n">
-        <v>0.6483546495437622</v>
+        <v>0.4557657837867737</v>
       </c>
       <c r="W4" t="n">
-        <v>0.7025578618049622</v>
+        <v>0.4403087794780731</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1850168</v>
+        <v>210159</v>
       </c>
       <c r="Z4" t="n">
-        <v>26773490</v>
+        <v>3006353</v>
       </c>
       <c r="AA4" t="n">
-        <v>744102</v>
+        <v>83023</v>
       </c>
       <c r="AB4" t="n">
-        <v>49580</v>
+        <v>5590</v>
       </c>
       <c r="AC4" t="n">
-        <v>10232</v>
+        <v>1131</v>
       </c>
       <c r="AD4" t="n">
-        <v>612</v>
+        <v>68</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1981098</v>
+        <v>224879</v>
       </c>
       <c r="AG4" t="n">
-        <v>2595194</v>
+        <v>289558</v>
       </c>
       <c r="AH4" t="n">
-        <v>1189293</v>
+        <v>132831</v>
       </c>
       <c r="AI4" t="n">
-        <v>271206</v>
+        <v>30385</v>
       </c>
       <c r="AJ4" t="n">
-        <v>449168</v>
+        <v>50066</v>
       </c>
       <c r="AK4" t="n">
-        <v>119309</v>
+        <v>13267</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9567735195159912</v>
+        <v>0.9561707377433777</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.910711407661438</v>
+        <v>0.9107076525688171</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.8578504323959351</v>
+        <v>0.8574937582015991</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.6615788340568542</v>
+        <v>0.660554051399231</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.9017512202262878</v>
+        <v>0.9015724062919617</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.931333601474762</v>
+        <v>0.9312376976013184</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>57</v>
+        <v>23</v>
       </c>
       <c r="D5" t="n">
-        <v>391474</v>
+        <v>94641</v>
       </c>
       <c r="E5" t="n">
-        <v>2429545</v>
+        <v>423483</v>
       </c>
       <c r="F5" t="n">
-        <v>4691092</v>
+        <v>304730</v>
       </c>
       <c r="G5" t="n">
-        <v>176845</v>
+        <v>32236</v>
       </c>
       <c r="H5" t="n">
-        <v>651880</v>
+        <v>76459</v>
       </c>
       <c r="I5" t="n">
-        <v>64548</v>
+        <v>8307</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>6433519</v>
+        <v>813147</v>
       </c>
       <c r="L5" t="n">
-        <v>9016279</v>
+        <v>1530799</v>
       </c>
       <c r="M5" t="n">
-        <v>3714349</v>
+        <v>635149</v>
       </c>
       <c r="N5" t="n">
-        <v>617116</v>
+        <v>81158</v>
       </c>
       <c r="O5" t="n">
-        <v>1694259</v>
+        <v>298210</v>
       </c>
       <c r="P5" t="n">
-        <v>630950</v>
+        <v>130398</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.999994158744812</v>
+        <v>0.9999871253967285</v>
       </c>
       <c r="R5" t="n">
-        <v>0.903779149055481</v>
+        <v>0.8612740039825439</v>
       </c>
       <c r="S5" t="n">
-        <v>0.8756357431411743</v>
+        <v>0.8250126242637634</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9545297622680664</v>
+        <v>0.9392568469047546</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9922528266906738</v>
+        <v>0.9881936311721802</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9785846471786499</v>
+        <v>0.9688235521316528</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9935886263847351</v>
+        <v>0.9901470541954041</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>72118</v>
+        <v>8098</v>
       </c>
       <c r="Z5" t="n">
-        <v>769074</v>
+        <v>86770</v>
       </c>
       <c r="AA5" t="n">
-        <v>7206453</v>
+        <v>805109</v>
       </c>
       <c r="AB5" t="n">
-        <v>89663</v>
+        <v>10018</v>
       </c>
       <c r="AC5" t="n">
-        <v>262436</v>
+        <v>29251</v>
       </c>
       <c r="AD5" t="n">
-        <v>5697</v>
+        <v>633</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1907757</v>
+        <v>211850</v>
       </c>
       <c r="AG5" t="n">
-        <v>2654694</v>
+        <v>299971</v>
       </c>
       <c r="AH5" t="n">
-        <v>1198988</v>
+        <v>134770</v>
       </c>
       <c r="AI5" t="n">
-        <v>272006</v>
+        <v>30478</v>
       </c>
       <c r="AJ5" t="n">
-        <v>452091</v>
+        <v>50554</v>
       </c>
       <c r="AK5" t="n">
-        <v>119732</v>
+        <v>13363</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.9734689593315125</v>
+        <v>0.9732553958892822</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.9641835689544678</v>
+        <v>0.9638981223106384</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.9837063550949097</v>
+        <v>0.9836125373840332</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9962940216064453</v>
+        <v>0.99627286195755</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9938513040542603</v>
+        <v>0.9938381910324097</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.9983691573143005</v>
+        <v>0.9983692169189453</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>120</v>
+        <v>20</v>
       </c>
       <c r="D6" t="n">
-        <v>129706</v>
+        <v>21829</v>
       </c>
       <c r="E6" t="n">
-        <v>182715</v>
+        <v>26079</v>
       </c>
       <c r="F6" t="n">
-        <v>199786</v>
+        <v>23423</v>
       </c>
       <c r="G6" t="n">
-        <v>185852</v>
+        <v>8539</v>
       </c>
       <c r="H6" t="n">
-        <v>95057</v>
+        <v>8738</v>
       </c>
       <c r="I6" t="n">
-        <v>9732</v>
+        <v>1069</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>58389</v>
+        <v>6586</v>
       </c>
       <c r="Z6" t="n">
-        <v>48057</v>
+        <v>5354</v>
       </c>
       <c r="AA6" t="n">
-        <v>98343</v>
+        <v>11038</v>
       </c>
       <c r="AB6" t="n">
-        <v>530962</v>
+        <v>59219</v>
       </c>
       <c r="AC6" t="n">
-        <v>62888</v>
+        <v>7019</v>
       </c>
       <c r="AD6" t="n">
-        <v>4329</v>
+        <v>481</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1260,25 +1260,25 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>113</v>
+        <v>57</v>
       </c>
       <c r="D7" t="n">
-        <v>31906</v>
+        <v>10317</v>
       </c>
       <c r="E7" t="n">
-        <v>334623</v>
+        <v>83253</v>
       </c>
       <c r="F7" t="n">
-        <v>886833</v>
+        <v>133832</v>
       </c>
       <c r="G7" t="n">
-        <v>223099</v>
+        <v>51802</v>
       </c>
       <c r="H7" t="n">
-        <v>2893818</v>
+        <v>213171</v>
       </c>
       <c r="I7" t="n">
-        <v>217685</v>
+        <v>18949</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>171</v>
+        <v>8</v>
       </c>
       <c r="Z7" t="n">
-        <v>7287</v>
+        <v>810</v>
       </c>
       <c r="AA7" t="n">
-        <v>267782</v>
+        <v>30010</v>
       </c>
       <c r="AB7" t="n">
-        <v>68450</v>
+        <v>7671</v>
       </c>
       <c r="AC7" t="n">
-        <v>4135986</v>
+        <v>460827</v>
       </c>
       <c r="AD7" t="n">
-        <v>108401</v>
+        <v>12055</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>123</v>
+        <v>80</v>
       </c>
       <c r="D8" t="n">
-        <v>1478</v>
+        <v>394</v>
       </c>
       <c r="E8" t="n">
-        <v>30598</v>
+        <v>8639</v>
       </c>
       <c r="F8" t="n">
-        <v>72169</v>
+        <v>16248</v>
       </c>
       <c r="G8" t="n">
-        <v>29305</v>
+        <v>9693</v>
       </c>
       <c r="H8" t="n">
-        <v>497277</v>
+        <v>95344</v>
       </c>
       <c r="I8" t="n">
-        <v>1109858</v>
+        <v>63288</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>252</v>
+        <v>28</v>
       </c>
       <c r="Z8" t="n">
-        <v>729</v>
+        <v>81</v>
       </c>
       <c r="AA8" t="n">
-        <v>2981</v>
+        <v>333</v>
       </c>
       <c r="AB8" t="n">
-        <v>2393</v>
+        <v>267</v>
       </c>
       <c r="AC8" t="n">
-        <v>113377</v>
+        <v>12654</v>
       </c>
       <c r="AD8" t="n">
-        <v>1621076</v>
+        <v>180323</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
